--- a/data/26-04-15_poisson_ratio.xlsx
+++ b/data/26-04-15_poisson_ratio.xlsx
@@ -22,6 +22,13 @@
     <sheet name="B_3" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="F_2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="C_4" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="D_1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="D_2" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="F_3" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="D_3" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="F_4" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="F_5" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="F_6" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,10 +466,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="B2" t="n">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,287 +478,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9174959043551179</v>
+        <v>-0.9901816707863137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="B3" t="n">
-        <v>595</v>
+        <v>555</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0356234096692112</v>
+        <v>0.02863961813842482</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03409090909090909</v>
+        <v>-0.03645833333333334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="B4" t="n">
-        <v>574</v>
+        <v>534</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07633587786259542</v>
+        <v>0.06205250596658711</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06818181818181818</v>
+        <v>-0.07291666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="B5" t="n">
-        <v>553</v>
+        <v>513</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1068702290076336</v>
+        <v>0.0954653937947494</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1022727272727273</v>
+        <v>-0.109375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="B6" t="n">
-        <v>532</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1526717557251908</v>
+        <v>0.1360381861575179</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1363636363636364</v>
+        <v>-0.1458333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>471</v>
       </c>
       <c r="C7" t="n">
-        <v>0.178117048346056</v>
+        <v>0.1694510739856802</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1704545454545454</v>
+        <v>-0.1822916666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="B8" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2213740458015267</v>
+        <v>0.2171837708830549</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2045454545454546</v>
+        <v>-0.21875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="B9" t="n">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2569974554707379</v>
+        <v>0.2410501193317423</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2386363636363636</v>
+        <v>-0.2552083333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="B10" t="n">
-        <v>448</v>
+        <v>408</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2951653944020356</v>
+        <v>0.2887828162291169</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2727272727272727</v>
+        <v>-0.2916666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="B11" t="n">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3307888040712468</v>
+        <v>0.315035799522673</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3068181818181818</v>
+        <v>-0.328125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="B12" t="n">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3740458015267176</v>
+        <v>0.3579952267303103</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3409090909090909</v>
+        <v>-0.3645833333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="B13" t="n">
-        <v>385</v>
+        <v>345</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4020356234096692</v>
+        <v>0.3937947494033413</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.375</v>
+        <v>-0.4010416666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="B14" t="n">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4300254452926209</v>
+        <v>0.4343675417661098</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4090909090909091</v>
+        <v>-0.4375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="B15" t="n">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4631043256997455</v>
+        <v>0.4701670644391408</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4431818181818182</v>
+        <v>-0.4739583333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="B16" t="n">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4987277353689568</v>
+        <v>0.5107398568019093</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4772727272727273</v>
+        <v>-0.5104166666666666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="B17" t="n">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5496183206106871</v>
+        <v>0.5346062052505967</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5113636363636364</v>
+        <v>-0.546875</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="B18" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5954198473282443</v>
+        <v>0.5608591885441527</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5454545454545454</v>
+        <v>-0.5833333333333334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>639</v>
+        <v>673</v>
       </c>
       <c r="B19" t="n">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6259541984732825</v>
+        <v>0.6062052505966588</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5795454545454546</v>
+        <v>-0.6197916666666666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>649</v>
+        <v>687</v>
       </c>
       <c r="B20" t="n">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6513994910941476</v>
+        <v>0.639618138424821</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6136363636363636</v>
+        <v>-0.65625</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>669</v>
+        <v>698</v>
       </c>
       <c r="B21" t="n">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7022900763358778</v>
+        <v>0.665871121718377</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6477272727272727</v>
+        <v>-0.6927083333333334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>686</v>
+        <v>717</v>
       </c>
       <c r="B22" t="n">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7455470737913485</v>
+        <v>0.7112171837708831</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6818181818181818</v>
+        <v>-0.7291666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -797,10 +804,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="B2" t="n">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -809,91 +816,91 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.623941257091493</v>
+        <v>-1.587276327527284</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B3" t="n">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04028436018957346</v>
+        <v>-0.02481389578163772</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05922165820642978</v>
+        <v>0.05862646566164154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B4" t="n">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.08530805687203792</v>
+        <v>-0.06451612903225806</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1184433164128596</v>
+        <v>0.1172529313232831</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B5" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1232227488151659</v>
+        <v>-0.1141439205955335</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1776649746192893</v>
+        <v>0.1758793969849246</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B6" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1635071090047393</v>
+        <v>-0.141439205955335</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2368866328257191</v>
+        <v>0.2345058626465662</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B7" t="n">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2109004739336493</v>
+        <v>-0.1761786600496278</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2961082910321489</v>
+        <v>0.2931323283082077</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B8" t="n">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2488151658767772</v>
+        <v>-0.2009925558312655</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3553299492385787</v>
+        <v>0.3517587939698493</v>
       </c>
     </row>
     <row r="9">
@@ -901,139 +908,139 @@
         <v>307</v>
       </c>
       <c r="B9" t="n">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2725118483412322</v>
+        <v>-0.2382133995037221</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4145516074450085</v>
+        <v>0.4103852596314908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B10" t="n">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2985781990521327</v>
+        <v>-0.28287841191067</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4737732656514382</v>
+        <v>0.4690117252931323</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B11" t="n">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3293838862559242</v>
+        <v>-0.3325062034739454</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5329949238578681</v>
+        <v>0.5276381909547738</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B12" t="n">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3649289099526066</v>
+        <v>-0.369727047146402</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5922165820642978</v>
+        <v>0.5862646566164154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B13" t="n">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.4123222748815166</v>
+        <v>-0.4044665012406948</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6514382402707276</v>
+        <v>0.644891122278057</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B14" t="n">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.4478672985781991</v>
+        <v>-0.4367245657568238</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7106598984771574</v>
+        <v>0.7035175879396985</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B15" t="n">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4928909952606635</v>
+        <v>-0.4813895781637717</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7698815566835872</v>
+        <v>0.7621440536013401</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B16" t="n">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.5284360189573459</v>
+        <v>-0.5086848635235732</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8291032148900169</v>
+        <v>0.8207705192629816</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B17" t="n">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.5687203791469194</v>
+        <v>-0.5359801488833746</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8883248730964467</v>
+        <v>0.8793969849246231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B18" t="n">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.6090047393364929</v>
+        <v>-0.5732009925558312</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9475465313028765</v>
+        <v>0.9380234505862647</v>
       </c>
     </row>
     <row r="19">
@@ -1041,55 +1048,55 @@
         <v>155</v>
       </c>
       <c r="B19" t="n">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.6327014218009479</v>
+        <v>-0.6153846153846154</v>
       </c>
       <c r="D19" t="n">
-        <v>1.006768189509306</v>
+        <v>0.9966499162479062</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B20" t="n">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.6635071090047393</v>
+        <v>-0.6575682382133995</v>
       </c>
       <c r="D20" t="n">
-        <v>1.065989847715736</v>
+        <v>1.055276381909548</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B21" t="n">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.7014218009478673</v>
+        <v>-0.6997518610421837</v>
       </c>
       <c r="D21" t="n">
-        <v>1.125211505922166</v>
+        <v>1.113902847571189</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B22" t="n">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.7417061611374408</v>
+        <v>-0.7270471464019851</v>
       </c>
       <c r="D22" t="n">
-        <v>1.184433164128596</v>
+        <v>1.172529313232831</v>
       </c>
     </row>
   </sheetData>
@@ -1135,10 +1142,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="B2" t="n">
-        <v>649</v>
+        <v>622</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1147,287 +1154,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.838694283514033</v>
+        <v>-1.717013396953904</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B3" t="n">
-        <v>689</v>
+        <v>662</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04166666666666666</v>
+        <v>-0.04071246819338423</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06163328197226502</v>
+        <v>0.06430868167202572</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B4" t="n">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0857843137254902</v>
+        <v>-0.0737913486005089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.12326656394453</v>
+        <v>0.1286173633440514</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B5" t="n">
-        <v>769</v>
+        <v>742</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1127450980392157</v>
+        <v>-0.1246819338422392</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1848998459167951</v>
+        <v>0.1929260450160772</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="B6" t="n">
-        <v>809</v>
+        <v>782</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1544117647058824</v>
+        <v>-0.1730279898218829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2465331278890601</v>
+        <v>0.2572347266881029</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="B7" t="n">
-        <v>849</v>
+        <v>822</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1862745098039216</v>
+        <v>-0.2086513994910942</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3081664098613251</v>
+        <v>0.3215434083601286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="B8" t="n">
-        <v>889</v>
+        <v>862</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2230392156862745</v>
+        <v>-0.2366412213740458</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3697996918335901</v>
+        <v>0.3858520900321543</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="B9" t="n">
-        <v>929</v>
+        <v>902</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2475490196078431</v>
+        <v>-0.267175572519084</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4314329738058552</v>
+        <v>0.4501607717041801</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="B10" t="n">
-        <v>969</v>
+        <v>942</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2720588235294117</v>
+        <v>-0.3002544529262087</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4930662557781202</v>
+        <v>0.5144694533762058</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="B11" t="n">
-        <v>1009</v>
+        <v>982</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2965686274509804</v>
+        <v>-0.3460559796437659</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5546995377503852</v>
+        <v>0.5787781350482315</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="B12" t="n">
-        <v>1049</v>
+        <v>1022</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3791348600508906</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6163328197226502</v>
+        <v>0.6430868167202572</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B13" t="n">
-        <v>1089</v>
+        <v>1062</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3725490196078431</v>
+        <v>-0.4198473282442748</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6779661016949152</v>
+        <v>0.707395498392283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B14" t="n">
-        <v>1129</v>
+        <v>1102</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.4117647058823529</v>
+        <v>-0.460559796437659</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7395993836671803</v>
+        <v>0.7717041800643086</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="B15" t="n">
-        <v>1169</v>
+        <v>1142</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4436274509803921</v>
+        <v>-0.4961832061068702</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8012326656394453</v>
+        <v>0.8360128617363344</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B16" t="n">
-        <v>1209</v>
+        <v>1182</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.4754901960784313</v>
+        <v>-0.5292620865139949</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8628659476117103</v>
+        <v>0.9003215434083601</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="B17" t="n">
-        <v>1249</v>
+        <v>1222</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.5098039215686274</v>
+        <v>-0.5776081424936387</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9244992295839753</v>
+        <v>0.9646302250803859</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B18" t="n">
-        <v>1289</v>
+        <v>1262</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.553921568627451</v>
+        <v>-0.6106870229007634</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9861325115562404</v>
+        <v>1.028938906752412</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="B19" t="n">
-        <v>1329</v>
+        <v>1302</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5882352941176471</v>
+        <v>-0.648854961832061</v>
       </c>
       <c r="D19" t="n">
-        <v>1.047765793528505</v>
+        <v>1.093247588424437</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="B20" t="n">
-        <v>1369</v>
+        <v>1342</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.6127450980392157</v>
+        <v>-0.6768447837150128</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10939907550077</v>
+        <v>1.157556270096463</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="B21" t="n">
-        <v>1409</v>
+        <v>1382</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.6544117647058824</v>
+        <v>-0.72264631043257</v>
       </c>
       <c r="D21" t="n">
-        <v>1.171032357473035</v>
+        <v>1.221864951768489</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="B22" t="n">
-        <v>1449</v>
+        <v>1422</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.6862745098039216</v>
+        <v>-0.7557251908396947</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2326656394453</v>
+        <v>1.286173633440514</v>
       </c>
     </row>
   </sheetData>
@@ -1811,10 +1818,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="B2" t="n">
-        <v>590</v>
+        <v>627</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1823,287 +1830,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.741305497954874</v>
+        <v>-0.7078537305457689</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="B3" t="n">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02619047619047619</v>
+        <v>0.05141388174807198</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0288135593220339</v>
+        <v>-0.02711323763955343</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="B4" t="n">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07380952380952381</v>
+        <v>0.07712082262210797</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0576271186440678</v>
+        <v>-0.05422647527910686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="B5" t="n">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1047619047619048</v>
+        <v>0.1285347043701799</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08644067796610169</v>
+        <v>-0.08133971291866028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="B6" t="n">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1523809523809524</v>
+        <v>0.1670951156812339</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1152542372881356</v>
+        <v>-0.1084529505582137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>504</v>
+        <v>465</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2</v>
+        <v>0.1953727506426735</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1440677966101695</v>
+        <v>-0.1355661881977671</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>517</v>
+        <v>481</v>
       </c>
       <c r="B8" t="n">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="C8" t="n">
-        <v>0.230952380952381</v>
+        <v>0.2365038560411311</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1728813559322034</v>
+        <v>-0.1626794258373206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>535</v>
+        <v>494</v>
       </c>
       <c r="B9" t="n">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.2699228791773779</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2016949152542373</v>
+        <v>-0.189792663476874</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>545</v>
+        <v>511</v>
       </c>
       <c r="B10" t="n">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.3136246786632391</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2305084745762712</v>
+        <v>-0.2169059011164274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>564</v>
+        <v>525</v>
       </c>
       <c r="B11" t="n">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.3496143958868895</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2593220338983051</v>
+        <v>-0.2440191387559809</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>578</v>
+        <v>544</v>
       </c>
       <c r="B12" t="n">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3761904761904762</v>
+        <v>0.3984575835475578</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.288135593220339</v>
+        <v>-0.2711323763955343</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="B13" t="n">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4119047619047619</v>
+        <v>0.4498714652956298</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3169491525423729</v>
+        <v>-0.2982456140350877</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="B14" t="n">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4547619047619048</v>
+        <v>0.4781491002570694</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3457627118644068</v>
+        <v>-0.3253588516746411</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>630</v>
+        <v>594</v>
       </c>
       <c r="B15" t="n">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>0.5269922879177378</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3745762711864407</v>
+        <v>-0.3524720893141946</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>645</v>
+        <v>606</v>
       </c>
       <c r="B16" t="n">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5578406169665809</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4033898305084746</v>
+        <v>-0.379585326953748</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>659</v>
+        <v>617</v>
       </c>
       <c r="B17" t="n">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="C17" t="n">
-        <v>0.569047619047619</v>
+        <v>0.5861182519280206</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4322033898305085</v>
+        <v>-0.4066985645933014</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>679</v>
+        <v>631</v>
       </c>
       <c r="B18" t="n">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.622107969151671</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4610169491525424</v>
+        <v>-0.4338118022328549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>692</v>
+        <v>644</v>
       </c>
       <c r="B19" t="n">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6476190476190476</v>
+        <v>0.6555269922879178</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4898305084745763</v>
+        <v>-0.4609250398724083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>711</v>
+        <v>664</v>
       </c>
       <c r="B20" t="n">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6928571428571428</v>
+        <v>0.7069408740359897</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5186440677966102</v>
+        <v>-0.4880382775119617</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>730</v>
+        <v>675</v>
       </c>
       <c r="B21" t="n">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.7352185089974294</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5474576271186441</v>
+        <v>-0.5151515151515151</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>747</v>
+        <v>686</v>
       </c>
       <c r="B22" t="n">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7785714285714286</v>
+        <v>0.7634961439588689</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.576271186440678</v>
+        <v>-0.5422647527910686</v>
       </c>
     </row>
   </sheetData>
@@ -2149,10 +2156,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="B2" t="n">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -2161,287 +2168,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4177860120426122</v>
+        <v>-0.5177945844916975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="B3" t="n">
-        <v>590</v>
+        <v>566</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03794037940379404</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01666666666666667</v>
+        <v>-0.01736111111111111</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="B4" t="n">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08130081300813008</v>
+        <v>0.0707070707070707</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.03472222222222222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="B5" t="n">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1165311653116531</v>
+        <v>0.1035353535353535</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.05208333333333334</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="B6" t="n">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1436314363143631</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.06944444444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="B7" t="n">
-        <v>550</v>
+        <v>526</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.1616161616161616</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08333333333333333</v>
+        <v>-0.08680555555555555</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="B8" t="n">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2303523035230352</v>
+        <v>0.2070707070707071</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>-0.1041666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="B9" t="n">
-        <v>530</v>
+        <v>506</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2655826558265583</v>
+        <v>0.2323232323232323</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1166666666666667</v>
+        <v>-0.1215277777777778</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="B10" t="n">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3143631436314363</v>
+        <v>0.2601010101010101</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1388888888888889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="B11" t="n">
-        <v>510</v>
+        <v>486</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3631436314363143</v>
+        <v>0.3005050505050505</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.15</v>
+        <v>-0.15625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B12" t="n">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4065040650406504</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.1736111111111111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B13" t="n">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4525745257452575</v>
+        <v>0.3686868686868687</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1833333333333333</v>
+        <v>-0.1909722222222222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B14" t="n">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5067750677506775</v>
+        <v>0.4141414141414141</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2</v>
+        <v>-0.2083333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B15" t="n">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5582655826558266</v>
+        <v>0.4570707070707071</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2166666666666667</v>
+        <v>-0.2256944444444444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B16" t="n">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5075757575757576</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.2430555555555556</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B17" t="n">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6260162601626016</v>
+        <v>0.5505050505050505</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.25</v>
+        <v>-0.2604166666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B18" t="n">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6747967479674797</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2777777777777778</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B19" t="n">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7046070460704607</v>
+        <v>0.601010101010101</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2833333333333333</v>
+        <v>-0.2951388888888889</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B20" t="n">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7479674796747967</v>
+        <v>0.6313131313131313</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3</v>
+        <v>-0.3125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B21" t="n">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7913279132791328</v>
+        <v>0.6792929292929293</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3166666666666667</v>
+        <v>-0.3298611111111111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="B22" t="n">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.7247474747474747</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -2515,7 +2522,6 @@
       <c r="D3" t="n">
         <v>0.06568144499178982</v>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2530,7 +2536,6 @@
       <c r="D4" t="n">
         <v>0.1313628899835796</v>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2545,7 +2550,6 @@
       <c r="D5" t="n">
         <v>0.1970443349753695</v>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2560,7 +2564,6 @@
       <c r="D6" t="n">
         <v>0.2627257799671593</v>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2575,7 +2578,6 @@
       <c r="D7" t="n">
         <v>0.3284072249589491</v>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2590,7 +2592,6 @@
       <c r="D8" t="n">
         <v>0.3940886699507389</v>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2605,7 +2606,6 @@
       <c r="D9" t="n">
         <v>0.4597701149425287</v>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2620,7 +2620,6 @@
       <c r="D10" t="n">
         <v>0.5254515599343186</v>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2635,7 +2634,6 @@
       <c r="D11" t="n">
         <v>0.5911330049261084</v>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2650,7 +2648,6 @@
       <c r="D12" t="n">
         <v>0.6568144499178982</v>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2665,7 +2662,6 @@
       <c r="D13" t="n">
         <v>0.722495894909688</v>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2680,7 +2676,6 @@
       <c r="D14" t="n">
         <v>0.7881773399014779</v>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2695,7 +2690,6 @@
       <c r="D15" t="n">
         <v>0.8538587848932676</v>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2710,7 +2704,6 @@
       <c r="D16" t="n">
         <v>0.9195402298850575</v>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2725,7 +2718,6 @@
       <c r="D17" t="n">
         <v>0.9852216748768473</v>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2740,7 +2732,6 @@
       <c r="D18" t="n">
         <v>1.050903119868637</v>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2755,7 +2746,6 @@
       <c r="D19" t="n">
         <v>1.116584564860427</v>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2770,7 +2760,6 @@
       <c r="D20" t="n">
         <v>1.182266009852217</v>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2785,7 +2774,6 @@
       <c r="D21" t="n">
         <v>1.247947454844007</v>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2800,7 +2788,1358 @@
       <c r="D22" t="n">
         <v>1.313628899835796</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lat_length</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trans_length method1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat_strain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trans_strain method1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>poisson method1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>357</v>
+      </c>
+      <c r="B2" t="n">
+        <v>643</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.8478493026350508</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>369</v>
+      </c>
+      <c r="B3" t="n">
+        <v>621</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03361344537815126</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03421461897356143</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>384</v>
+      </c>
+      <c r="B4" t="n">
+        <v>599</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.07563025210084033</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06842923794712286</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>394</v>
+      </c>
+      <c r="B5" t="n">
+        <v>577</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1036414565826331</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1026438569206843</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>412</v>
+      </c>
+      <c r="B6" t="n">
+        <v>555</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15406162464986</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1368584758942457</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>425</v>
+      </c>
+      <c r="B7" t="n">
+        <v>533</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1710730948678071</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>441</v>
+      </c>
+      <c r="B8" t="n">
+        <v>511</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2052877138413686</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>457</v>
+      </c>
+      <c r="B9" t="n">
+        <v>489</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2801120448179272</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.23950233281493</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>468</v>
+      </c>
+      <c r="B10" t="n">
+        <v>467</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3109243697478992</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2737169517884914</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>483</v>
+      </c>
+      <c r="B11" t="n">
+        <v>445</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3079315707620529</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>423</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.4005602240896359</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3421461897356143</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>514</v>
+      </c>
+      <c r="B13" t="n">
+        <v>401</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4397759103641457</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3763608087091758</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>528</v>
+      </c>
+      <c r="B14" t="n">
+        <v>379</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4789915966386555</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.4105754276827372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>542</v>
+      </c>
+      <c r="B15" t="n">
+        <v>357</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5182072829131653</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.4447900466562986</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>553</v>
+      </c>
+      <c r="B16" t="n">
+        <v>335</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.47900466562986</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>563</v>
+      </c>
+      <c r="B17" t="n">
+        <v>313</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5770308123249299</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5132192846034215</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>580</v>
+      </c>
+      <c r="B18" t="n">
+        <v>291</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6246498599439776</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5474339035769828</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>590</v>
+      </c>
+      <c r="B19" t="n">
+        <v>269</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6526610644257703</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5816485225505443</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>602</v>
+      </c>
+      <c r="B20" t="n">
+        <v>247</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.6158631415241057</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>617</v>
+      </c>
+      <c r="B21" t="n">
+        <v>225</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7282913165266106</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.6500777604976672</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>636</v>
+      </c>
+      <c r="B22" t="n">
+        <v>203</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7815126050420168</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.6842923794712286</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lat_length</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trans_length method1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat_strain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trans_strain method1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>poisson method1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B2" t="n">
+        <v>639</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.8302934406958746</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>404</v>
+      </c>
+      <c r="B3" t="n">
+        <v>617</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03061224489795918</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03442879499217527</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>415</v>
+      </c>
+      <c r="B4" t="n">
+        <v>595</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0586734693877551</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06885758998435054</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>430</v>
+      </c>
+      <c r="B5" t="n">
+        <v>573</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.09693877551020408</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1032863849765258</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>448</v>
+      </c>
+      <c r="B6" t="n">
+        <v>551</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1377151799687011</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>463</v>
+      </c>
+      <c r="B7" t="n">
+        <v>529</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1811224489795918</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1721439749608764</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>482</v>
+      </c>
+      <c r="B8" t="n">
+        <v>507</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2295918367346939</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2065727699530517</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>502</v>
+      </c>
+      <c r="B9" t="n">
+        <v>485</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2806122448979592</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2410015649452269</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>517</v>
+      </c>
+      <c r="B10" t="n">
+        <v>463</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3188775510204082</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2754303599374022</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>529</v>
+      </c>
+      <c r="B11" t="n">
+        <v>441</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3494897959183674</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3098591549295774</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>544</v>
+      </c>
+      <c r="B12" t="n">
+        <v>419</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3877551020408163</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3442879499217527</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>560</v>
+      </c>
+      <c r="B13" t="n">
+        <v>397</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.378716744913928</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>577</v>
+      </c>
+      <c r="B14" t="n">
+        <v>375</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4719387755102041</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.4131455399061033</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>592</v>
+      </c>
+      <c r="B15" t="n">
+        <v>353</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5102040816326531</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.4475743348982786</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>603</v>
+      </c>
+      <c r="B16" t="n">
+        <v>331</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5382653061224489</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.4820031298904539</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>621</v>
+      </c>
+      <c r="B17" t="n">
+        <v>309</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5841836734693877</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5164319248826291</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>636</v>
+      </c>
+      <c r="B18" t="n">
+        <v>287</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6224489795918368</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5508607198748043</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>647</v>
+      </c>
+      <c r="B19" t="n">
+        <v>265</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6505102040816326</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5852895148669797</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>663</v>
+      </c>
+      <c r="B20" t="n">
+        <v>243</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6913265306122449</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.6197183098591549</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>678</v>
+      </c>
+      <c r="B21" t="n">
+        <v>221</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7295918367346939</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.6541471048513302</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>698</v>
+      </c>
+      <c r="B22" t="n">
+        <v>199</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7806122448979592</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.6885758998435054</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lat_length</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trans_length method1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat_strain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trans_strain method1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>poisson method1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>417</v>
+      </c>
+      <c r="B2" t="n">
+        <v>588</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.4390543867306186</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>427</v>
+      </c>
+      <c r="B3" t="n">
+        <v>578</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.02398081534772182</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.01700680272108844</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>438</v>
+      </c>
+      <c r="B4" t="n">
+        <v>568</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.05035971223021583</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03401360544217687</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>456</v>
+      </c>
+      <c r="B5" t="n">
+        <v>558</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.09352517985611511</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.05102040816326531</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>476</v>
+      </c>
+      <c r="B6" t="n">
+        <v>548</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1414868105515588</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.06802721088435375</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>493</v>
+      </c>
+      <c r="B7" t="n">
+        <v>538</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1822541966426859</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.08503401360544217</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>512</v>
+      </c>
+      <c r="B8" t="n">
+        <v>528</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2278177458033573</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1020408163265306</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>522</v>
+      </c>
+      <c r="B9" t="n">
+        <v>518</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2517985611510791</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.119047619047619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>542</v>
+      </c>
+      <c r="B10" t="n">
+        <v>508</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2997601918465228</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1360544217687075</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>552</v>
+      </c>
+      <c r="B11" t="n">
+        <v>498</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3237410071942446</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1530612244897959</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>568</v>
+      </c>
+      <c r="B12" t="n">
+        <v>488</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3621103117505995</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1700680272108843</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>587</v>
+      </c>
+      <c r="B13" t="n">
+        <v>478</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.407673860911271</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1870748299319728</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>600</v>
+      </c>
+      <c r="B14" t="n">
+        <v>468</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4388489208633093</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2040816326530612</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>611</v>
+      </c>
+      <c r="B15" t="n">
+        <v>458</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4652278177458034</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2210884353741497</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>622</v>
+      </c>
+      <c r="B16" t="n">
+        <v>448</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4916067146282974</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.2380952380952381</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>640</v>
+      </c>
+      <c r="B17" t="n">
+        <v>438</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5347721822541966</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.2551020408163265</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>658</v>
+      </c>
+      <c r="B18" t="n">
+        <v>428</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5779376498800959</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.272108843537415</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>670</v>
+      </c>
+      <c r="B19" t="n">
+        <v>418</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6067146282973621</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2891156462585034</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>680</v>
+      </c>
+      <c r="B20" t="n">
+        <v>408</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6306954436450839</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.3061224489795918</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>691</v>
+      </c>
+      <c r="B21" t="n">
+        <v>398</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.657074340527578</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.3231292517006803</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>705</v>
+      </c>
+      <c r="B22" t="n">
+        <v>388</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6906474820143885</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.3401360544217687</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lat_length</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trans_length method1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat_strain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trans_strain method1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>poisson method1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>416</v>
+      </c>
+      <c r="B2" t="n">
+        <v>617</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.9595165311328099</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>428</v>
+      </c>
+      <c r="B3" t="n">
+        <v>595</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.02884615384615385</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03565640194489465</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>440</v>
+      </c>
+      <c r="B4" t="n">
+        <v>573</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.07131280388978931</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>457</v>
+      </c>
+      <c r="B5" t="n">
+        <v>551</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0985576923076923</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.106969205834684</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>475</v>
+      </c>
+      <c r="B6" t="n">
+        <v>529</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1418269230769231</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1426256077795786</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>488</v>
+      </c>
+      <c r="B7" t="n">
+        <v>507</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1730769230769231</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1782820097244733</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>485</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2019230769230769</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2139384116693679</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>520</v>
+      </c>
+      <c r="B9" t="n">
+        <v>463</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2495948136142626</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>536</v>
+      </c>
+      <c r="B10" t="n">
+        <v>441</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2884615384615384</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2852512155591572</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>549</v>
+      </c>
+      <c r="B11" t="n">
+        <v>419</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3197115384615384</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3209076175040519</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>566</v>
+      </c>
+      <c r="B12" t="n">
+        <v>397</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3605769230769231</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3565640194489465</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>585</v>
+      </c>
+      <c r="B13" t="n">
+        <v>375</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3922204213938412</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>601</v>
+      </c>
+      <c r="B14" t="n">
+        <v>353</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4447115384615384</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.4278768233387358</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>614</v>
+      </c>
+      <c r="B15" t="n">
+        <v>331</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4759615384615384</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.4635332252836304</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>633</v>
+      </c>
+      <c r="B16" t="n">
+        <v>309</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5216346153846154</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.4991896272285251</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>644</v>
+      </c>
+      <c r="B17" t="n">
+        <v>287</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5480769230769231</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5348460291734197</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>655</v>
+      </c>
+      <c r="B18" t="n">
+        <v>265</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5745192307692307</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5705024311183144</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>673</v>
+      </c>
+      <c r="B19" t="n">
+        <v>243</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6177884615384616</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.6061588330632091</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>691</v>
+      </c>
+      <c r="B20" t="n">
+        <v>221</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6610576923076923</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.6418152350081038</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>705</v>
+      </c>
+      <c r="B21" t="n">
+        <v>199</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6947115384615384</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.6774716369529984</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>716</v>
+      </c>
+      <c r="B22" t="n">
+        <v>177</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7211538461538461</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.713128038897893</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2845,10 +4184,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="B2" t="n">
-        <v>594</v>
+        <v>557</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -2857,287 +4196,1301 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7655973452186524</v>
+        <v>-0.8502705121145288</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="B3" t="n">
-        <v>577</v>
+        <v>540</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02427184466019417</v>
+        <v>0.02352941176470588</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02861952861952862</v>
+        <v>-0.03052064631956912</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="B4" t="n">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04854368932038835</v>
+        <v>0.05176470588235294</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05723905723905724</v>
+        <v>-0.06104129263913824</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B5" t="n">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08009708737864078</v>
+        <v>0.09411764705882353</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08585858585858586</v>
+        <v>-0.09156193895870736</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="B6" t="n">
-        <v>526</v>
+        <v>489</v>
       </c>
       <c r="C6" t="n">
-        <v>0.116504854368932</v>
+        <v>0.131764705882353</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1144781144781145</v>
+        <v>-0.1220825852782765</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="B7" t="n">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1553398058252427</v>
+        <v>0.1694117647058823</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1430976430976431</v>
+        <v>-0.1526032315978456</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="B8" t="n">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1990291262135922</v>
+        <v>0.2023529411764706</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1717171717171717</v>
+        <v>-0.1831238779174147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B9" t="n">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2427184466019418</v>
+        <v>0.2305882352941176</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2003367003367003</v>
+        <v>-0.2136445242369839</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B10" t="n">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2839805825242718</v>
+        <v>0.2611764705882353</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.228956228956229</v>
+        <v>-0.244165170556553</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="B11" t="n">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3131067961165049</v>
+        <v>0.3082352941176471</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2575757575757576</v>
+        <v>-0.2746858168761221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="B12" t="n">
-        <v>424</v>
+        <v>387</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3470873786407767</v>
+        <v>0.3435294117647059</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2861952861952862</v>
+        <v>-0.3052064631956912</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="B13" t="n">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3810679611650485</v>
+        <v>0.3858823529411765</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3148148148148148</v>
+        <v>-0.3357271095152603</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B14" t="n">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4223300970873786</v>
+        <v>0.4258823529411765</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3434343434343434</v>
+        <v>-0.3662477558348294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="B15" t="n">
-        <v>373</v>
+        <v>336</v>
       </c>
       <c r="C15" t="n">
-        <v>0.470873786407767</v>
+        <v>0.4494117647058823</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3720538720538721</v>
+        <v>-0.3967684021543986</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B16" t="n">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5048543689320388</v>
+        <v>0.4729411764705883</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4006734006734007</v>
+        <v>-0.4272890484739677</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B17" t="n">
-        <v>339</v>
+        <v>302</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5533980582524272</v>
+        <v>0.5152941176470588</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4292929292929293</v>
+        <v>-0.4578096947935368</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="B18" t="n">
-        <v>322</v>
+        <v>285</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5800970873786407</v>
+        <v>0.5529411764705883</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4579124579124579</v>
+        <v>-0.4883303411131059</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B19" t="n">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6262135922330098</v>
+        <v>0.5788235294117647</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4865319865319865</v>
+        <v>-0.518850987432675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B20" t="n">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="C20" t="n">
-        <v>0.662621359223301</v>
+        <v>0.6164705882352941</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5151515151515151</v>
+        <v>-0.5493716337522442</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B21" t="n">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7014563106796117</v>
+        <v>0.6447058823529411</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5437710437710438</v>
+        <v>-0.5798922800718133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7475728155339806</v>
+        <v>0.6729411764705883</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5723905723905723</v>
+        <v>-0.6104129263913824</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lat_length</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trans_length method1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat_strain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trans_strain method1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>poisson method1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>361</v>
+      </c>
+      <c r="B2" t="n">
+        <v>620</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.3514781307474251</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>374</v>
+      </c>
+      <c r="B3" t="n">
+        <v>610</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03601108033240998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.01612903225806452</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>387</v>
+      </c>
+      <c r="B4" t="n">
+        <v>600</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.07202216066481995</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03225806451612903</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>399</v>
+      </c>
+      <c r="B5" t="n">
+        <v>590</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.04838709677419355</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>419</v>
+      </c>
+      <c r="B6" t="n">
+        <v>580</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1606648199445983</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.06451612903225806</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>434</v>
+      </c>
+      <c r="B7" t="n">
+        <v>570</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2022160664819945</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.08064516129032258</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>452</v>
+      </c>
+      <c r="B8" t="n">
+        <v>560</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2520775623268698</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.09677419354838709</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>469</v>
+      </c>
+      <c r="B9" t="n">
+        <v>550</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2991689750692521</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1129032258064516</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>489</v>
+      </c>
+      <c r="B10" t="n">
+        <v>540</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3545706371191136</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1290322580645161</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>502</v>
+      </c>
+      <c r="B11" t="n">
+        <v>530</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3905817174515235</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1451612903225807</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>515</v>
+      </c>
+      <c r="B12" t="n">
+        <v>520</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.4265927977839335</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1612903225806452</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>525</v>
+      </c>
+      <c r="B13" t="n">
+        <v>510</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4542936288088643</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1774193548387097</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>540</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4958448753462604</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1935483870967742</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>555</v>
+      </c>
+      <c r="B15" t="n">
+        <v>490</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5373961218836565</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2096774193548387</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>568</v>
+      </c>
+      <c r="B16" t="n">
+        <v>480</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5734072022160664</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.2258064516129032</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>582</v>
+      </c>
+      <c r="B17" t="n">
+        <v>470</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6121883656509696</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.2419354838709677</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>594</v>
+      </c>
+      <c r="B18" t="n">
+        <v>460</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6454293628808865</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2580645161290323</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>612</v>
+      </c>
+      <c r="B19" t="n">
+        <v>450</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6952908587257618</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2741935483870968</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>622</v>
+      </c>
+      <c r="B20" t="n">
+        <v>440</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7229916897506925</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.2903225806451613</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>635</v>
+      </c>
+      <c r="B21" t="n">
+        <v>430</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7590027700831025</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.3064516129032258</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>654</v>
+      </c>
+      <c r="B22" t="n">
+        <v>420</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8116343490304709</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.3225806451612903</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lat_length</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trans_length method1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat_strain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trans_strain method1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>poisson method1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>446</v>
+      </c>
+      <c r="B2" t="n">
+        <v>606</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.4971795916960039</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>457</v>
+      </c>
+      <c r="B3" t="n">
+        <v>596</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.02466367713004484</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0165016501650165</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>471</v>
+      </c>
+      <c r="B4" t="n">
+        <v>586</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.05605381165919283</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.033003300330033</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>483</v>
+      </c>
+      <c r="B5" t="n">
+        <v>576</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08295964125560538</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.04950495049504951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>493</v>
+      </c>
+      <c r="B6" t="n">
+        <v>566</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1053811659192825</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.066006600660066</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>506</v>
+      </c>
+      <c r="B7" t="n">
+        <v>556</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1345291479820628</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.08250825082508251</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>522</v>
+      </c>
+      <c r="B8" t="n">
+        <v>546</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1704035874439462</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.09900990099009901</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>538</v>
+      </c>
+      <c r="B9" t="n">
+        <v>536</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2062780269058296</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1155115511551155</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>558</v>
+      </c>
+      <c r="B10" t="n">
+        <v>526</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2511210762331839</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.132013201320132</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>570</v>
+      </c>
+      <c r="B11" t="n">
+        <v>516</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2780269058295964</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1485148514851485</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>589</v>
+      </c>
+      <c r="B12" t="n">
+        <v>506</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3206278026905829</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.165016501650165</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>602</v>
+      </c>
+      <c r="B13" t="n">
+        <v>496</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3497757847533632</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1815181518151815</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>615</v>
+      </c>
+      <c r="B14" t="n">
+        <v>486</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3789237668161435</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.198019801980198</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>625</v>
+      </c>
+      <c r="B15" t="n">
+        <v>476</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4013452914798206</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2145214521452145</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>643</v>
+      </c>
+      <c r="B16" t="n">
+        <v>466</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4417040358744395</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.231023102310231</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>660</v>
+      </c>
+      <c r="B17" t="n">
+        <v>456</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4798206278026906</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.2475247524752475</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>677</v>
+      </c>
+      <c r="B18" t="n">
+        <v>446</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5179372197309418</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.264026402640264</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>694</v>
+      </c>
+      <c r="B19" t="n">
+        <v>436</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5560538116591929</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2805280528052805</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>709</v>
+      </c>
+      <c r="B20" t="n">
+        <v>426</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5896860986547086</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.297029702970297</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>722</v>
+      </c>
+      <c r="B21" t="n">
+        <v>416</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6188340807174888</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.3135313531353136</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>741</v>
+      </c>
+      <c r="B22" t="n">
+        <v>406</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6614349775784754</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.33003300330033</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lat_length</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trans_length method1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lat_strain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>trans_strain method1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>poisson method1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B2" t="n">
+        <v>551</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.5730461154929849</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>403</v>
+      </c>
+      <c r="B3" t="n">
+        <v>541</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.02806122448979592</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.01814882032667877</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>415</v>
+      </c>
+      <c r="B4" t="n">
+        <v>531</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0586734693877551</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03629764065335753</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>426</v>
+      </c>
+      <c r="B5" t="n">
+        <v>521</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08673469387755102</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.0544464609800363</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>438</v>
+      </c>
+      <c r="B6" t="n">
+        <v>511</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1173469387755102</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07259528130671507</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>452</v>
+      </c>
+      <c r="B7" t="n">
+        <v>501</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1530612244897959</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.09074410163339383</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>462</v>
+      </c>
+      <c r="B8" t="n">
+        <v>491</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1088929219600726</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>473</v>
+      </c>
+      <c r="B9" t="n">
+        <v>481</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2066326530612245</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1270417422867514</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>483</v>
+      </c>
+      <c r="B10" t="n">
+        <v>471</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2321428571428572</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1451905626134301</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>499</v>
+      </c>
+      <c r="B11" t="n">
+        <v>461</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2729591836734694</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1633393829401089</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>513</v>
+      </c>
+      <c r="B12" t="n">
+        <v>451</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3086734693877551</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1814882032667877</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>524</v>
+      </c>
+      <c r="B13" t="n">
+        <v>441</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.336734693877551</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1996370235934664</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>543</v>
+      </c>
+      <c r="B14" t="n">
+        <v>431</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3852040816326531</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2177858439201452</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>559</v>
+      </c>
+      <c r="B15" t="n">
+        <v>421</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4260204081632653</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.235934664246824</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>571</v>
+      </c>
+      <c r="B16" t="n">
+        <v>411</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4566326530612245</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.2540834845735027</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>581</v>
+      </c>
+      <c r="B17" t="n">
+        <v>401</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4821428571428572</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.2722323049001815</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>595</v>
+      </c>
+      <c r="B18" t="n">
+        <v>391</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5178571428571429</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2903811252268603</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>608</v>
+      </c>
+      <c r="B19" t="n">
+        <v>381</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5510204081632653</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.308529945553539</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>628</v>
+      </c>
+      <c r="B20" t="n">
+        <v>371</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6020408163265306</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.3266787658802178</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>646</v>
+      </c>
+      <c r="B21" t="n">
+        <v>361</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6479591836734694</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.3448275862068966</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>656</v>
+      </c>
+      <c r="B22" t="n">
+        <v>351</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.673469387755102</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.3629764065335753</v>
       </c>
     </row>
   </sheetData>
@@ -3183,10 +5536,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>397</v>
+        <v>446</v>
       </c>
       <c r="B2" t="n">
-        <v>593</v>
+        <v>634</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -3195,287 +5548,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.819871028268891</v>
+        <v>-1.799169280996529</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>381</v>
+        <v>433</v>
       </c>
       <c r="B3" t="n">
-        <v>633</v>
+        <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04030226700251889</v>
+        <v>-0.02914798206278027</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06745362563237774</v>
+        <v>0.06309148264984227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>368</v>
+        <v>423</v>
       </c>
       <c r="B4" t="n">
-        <v>673</v>
+        <v>714</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.07304785894206549</v>
+        <v>-0.0515695067264574</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1349072512647555</v>
+        <v>0.1261829652996845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="B5" t="n">
-        <v>713</v>
+        <v>754</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.110831234256927</v>
+        <v>-0.07623318385650224</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2023608768971332</v>
+        <v>0.1892744479495268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="B6" t="n">
-        <v>753</v>
+        <v>794</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1536523929471033</v>
+        <v>-0.1143497757847534</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2698145025295109</v>
+        <v>0.2523659305993691</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>316</v>
+        <v>385</v>
       </c>
       <c r="B7" t="n">
-        <v>793</v>
+        <v>834</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2040302267002519</v>
+        <v>-0.1367713004484305</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3372681281618887</v>
+        <v>0.3154574132492113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>299</v>
+        <v>370</v>
       </c>
       <c r="B8" t="n">
-        <v>833</v>
+        <v>874</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2468513853904282</v>
+        <v>-0.1704035874439462</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4047217537942664</v>
+        <v>0.3785488958990536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="B9" t="n">
-        <v>873</v>
+        <v>914</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2871536523929471</v>
+        <v>-0.2152466367713005</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4721753794266442</v>
+        <v>0.4416403785488959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="B10" t="n">
-        <v>913</v>
+        <v>954</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3249370277078086</v>
+        <v>-0.2533632286995516</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5396290050590219</v>
+        <v>0.5047318611987381</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="B11" t="n">
-        <v>953</v>
+        <v>994</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3677581863979849</v>
+        <v>-0.2937219730941704</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6070826306913997</v>
+        <v>0.5678233438485805</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>235</v>
+        <v>304</v>
       </c>
       <c r="B12" t="n">
-        <v>993</v>
+        <v>1034</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.4080604534005038</v>
+        <v>-0.3183856502242152</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6745362563237775</v>
+        <v>0.6309148264984227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>223</v>
+        <v>291</v>
       </c>
       <c r="B13" t="n">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.438287153652393</v>
+        <v>-0.3475336322869955</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7419898819561551</v>
+        <v>0.694006309148265</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="B14" t="n">
-        <v>1073</v>
+        <v>1114</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.4836272040302267</v>
+        <v>-0.3856502242152466</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8094435075885329</v>
+        <v>0.7570977917981072</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="B15" t="n">
-        <v>1113</v>
+        <v>1154</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.5088161209068011</v>
+        <v>-0.4260089686098655</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8768971332209107</v>
+        <v>0.8201892744479495</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="B16" t="n">
-        <v>1153</v>
+        <v>1194</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.5390428211586902</v>
+        <v>-0.4573991031390134</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9443507588532883</v>
+        <v>0.8832807570977917</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="B17" t="n">
-        <v>1193</v>
+        <v>1234</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.5717884130982368</v>
+        <v>-0.484304932735426</v>
       </c>
       <c r="D17" t="n">
-        <v>1.011804384485666</v>
+        <v>0.9463722397476341</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>160</v>
+        <v>212</v>
       </c>
       <c r="B18" t="n">
-        <v>1233</v>
+        <v>1274</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.5969773299748111</v>
+        <v>-0.5246636771300448</v>
       </c>
       <c r="D18" t="n">
-        <v>1.079258010118044</v>
+        <v>1.009463722397476</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="B19" t="n">
-        <v>1273</v>
+        <v>1314</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.6297229219143576</v>
+        <v>-0.5695067264573991</v>
       </c>
       <c r="D19" t="n">
-        <v>1.146711635750422</v>
+        <v>1.072555205047319</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="B20" t="n">
-        <v>1313</v>
+        <v>1354</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.6750629722921915</v>
+        <v>-0.6076233183856502</v>
       </c>
       <c r="D20" t="n">
-        <v>1.214165261382799</v>
+        <v>1.135646687697161</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="B21" t="n">
-        <v>1353</v>
+        <v>1394</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.7128463476070529</v>
+        <v>-0.6524663677130045</v>
       </c>
       <c r="D21" t="n">
-        <v>1.281618887015177</v>
+        <v>1.198738170347003</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="B22" t="n">
-        <v>1393</v>
+        <v>1434</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.7380352644836272</v>
+        <v>-0.6860986547085202</v>
       </c>
       <c r="D22" t="n">
-        <v>1.349072512647555</v>
+        <v>1.261829652996845</v>
       </c>
     </row>
   </sheetData>
@@ -3521,10 +5874,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>430</v>
+        <v>392</v>
       </c>
       <c r="B2" t="n">
-        <v>572</v>
+        <v>628</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -3533,287 +5886,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4734460474184455</v>
+        <v>-0.4507626481678357</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c r="B3" t="n">
-        <v>562</v>
+        <v>618</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02325581395348837</v>
+        <v>0.03826530612244898</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01748251748251748</v>
+        <v>-0.01592356687898089</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="B4" t="n">
-        <v>552</v>
+        <v>608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05813953488372093</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03496503496503497</v>
+        <v>-0.03184713375796178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="B5" t="n">
-        <v>542</v>
+        <v>598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09534883720930233</v>
+        <v>0.1224489795918367</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05244755244755245</v>
+        <v>-0.04777070063694268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="B6" t="n">
-        <v>532</v>
+        <v>588</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1209302325581395</v>
+        <v>0.1556122448979592</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06993006993006994</v>
+        <v>-0.06369426751592357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="B7" t="n">
-        <v>522</v>
+        <v>578</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1627906976744186</v>
+        <v>0.1913265306122449</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08741258741258741</v>
+        <v>-0.07961783439490445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="B8" t="n">
-        <v>512</v>
+        <v>568</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2</v>
+        <v>0.2346938775510204</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1048951048951049</v>
+        <v>-0.09554140127388536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="B9" t="n">
-        <v>502</v>
+        <v>558</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2348837209302325</v>
+        <v>0.2602040816326531</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1223776223776224</v>
+        <v>-0.1114649681528662</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>546</v>
+        <v>507</v>
       </c>
       <c r="B10" t="n">
-        <v>492</v>
+        <v>548</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2697674418604651</v>
+        <v>0.2933673469387755</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1398601398601399</v>
+        <v>-0.1273885350318471</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>565</v>
+        <v>520</v>
       </c>
       <c r="B11" t="n">
-        <v>482</v>
+        <v>538</v>
       </c>
       <c r="C11" t="n">
-        <v>0.313953488372093</v>
+        <v>0.3265306122448979</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1573426573426573</v>
+        <v>-0.143312101910828</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>585</v>
+        <v>537</v>
       </c>
       <c r="B12" t="n">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3604651162790697</v>
+        <v>0.3698979591836735</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1748251748251748</v>
+        <v>-0.1592356687898089</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>604</v>
+        <v>548</v>
       </c>
       <c r="B13" t="n">
-        <v>462</v>
+        <v>518</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4046511627906977</v>
+        <v>0.3979591836734694</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1923076923076923</v>
+        <v>-0.1751592356687898</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>616</v>
+        <v>559</v>
       </c>
       <c r="B14" t="n">
-        <v>452</v>
+        <v>508</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4325581395348837</v>
+        <v>0.4260204081632653</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2097902097902098</v>
+        <v>-0.1910828025477707</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>634</v>
+        <v>576</v>
       </c>
       <c r="B15" t="n">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4744186046511628</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2272727272727273</v>
+        <v>-0.2070063694267516</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>646</v>
+        <v>589</v>
       </c>
       <c r="B16" t="n">
-        <v>432</v>
+        <v>488</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5023255813953489</v>
+        <v>0.5025510204081632</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2447552447552448</v>
+        <v>-0.2229299363057325</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>660</v>
+        <v>602</v>
       </c>
       <c r="B17" t="n">
-        <v>422</v>
+        <v>478</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5348837209302325</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2622377622377622</v>
+        <v>-0.2388535031847134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>678</v>
+        <v>621</v>
       </c>
       <c r="B18" t="n">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5767441860465117</v>
+        <v>0.5841836734693877</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2797202797202797</v>
+        <v>-0.2547770700636943</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>694</v>
+        <v>637</v>
       </c>
       <c r="B19" t="n">
-        <v>402</v>
+        <v>458</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6139534883720931</v>
+        <v>0.625</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2972027972027972</v>
+        <v>-0.2707006369426752</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>711</v>
+        <v>655</v>
       </c>
       <c r="B20" t="n">
-        <v>392</v>
+        <v>448</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6534883720930232</v>
+        <v>0.6709183673469388</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3146853146853147</v>
+        <v>-0.286624203821656</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>730</v>
+        <v>665</v>
       </c>
       <c r="B21" t="n">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3321678321678322</v>
+        <v>-0.3025477707006369</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>741</v>
+        <v>675</v>
       </c>
       <c r="B22" t="n">
-        <v>372</v>
+        <v>428</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7232558139534884</v>
+        <v>0.7219387755102041</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3496503496503496</v>
+        <v>-0.3184713375796178</v>
       </c>
     </row>
   </sheetData>
@@ -3859,10 +6212,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B2" t="n">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -3871,288 +6224,308 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8961042464792529</v>
+        <v>-0.86436487483267</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B3" t="n">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04395604395604396</v>
+        <v>0.03932584269662921</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03488372093023256</v>
-      </c>
+        <v>-0.03523489932885906</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B4" t="n">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07303370786516854</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06976744186046512</v>
-      </c>
+        <v>-0.07046979865771812</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="B5" t="n">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.1095505617977528</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1046511627906977</v>
-      </c>
+        <v>-0.1057046979865772</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B6" t="n">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1601123595505618</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1395348837209302</v>
-      </c>
+        <v>-0.1409395973154362</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2005494505494506</v>
+        <v>0.199438202247191</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1744186046511628</v>
-      </c>
+        <v>-0.1761744966442953</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B8" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C8" t="n">
-        <v>0.239010989010989</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2093023255813954</v>
-      </c>
+        <v>-0.2114093959731544</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="B9" t="n">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2441860465116279</v>
-      </c>
+        <v>-0.2466442953020134</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B10" t="n">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3104395604395604</v>
+        <v>0.3202247191011236</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2790697674418605</v>
-      </c>
+        <v>-0.2818791946308725</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B11" t="n">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3543956043956044</v>
+        <v>0.3651685393258427</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.313953488372093</v>
-      </c>
+        <v>-0.3171140939597316</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B12" t="n">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3901098901098901</v>
+        <v>0.4157303370786517</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3488372093023256</v>
-      </c>
+        <v>-0.3523489932885906</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B13" t="n">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4634831460674158</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3837209302325582</v>
-      </c>
+        <v>-0.3875838926174497</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B14" t="n">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4807692307692308</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4186046511627907</v>
-      </c>
+        <v>-0.4228187919463087</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B15" t="n">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5561797752808989</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4534883720930232</v>
-      </c>
+        <v>-0.4580536912751678</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B16" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5604395604395604</v>
+        <v>0.5926966292134831</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4883720930232558</v>
-      </c>
+        <v>-0.4932885906040269</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B17" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5934065934065934</v>
+        <v>0.6207865168539326</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5232558139534884</v>
-      </c>
+        <v>-0.5285234899328859</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B18" t="n">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6346153846153846</v>
+        <v>0.6573033707865169</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5581395348837209</v>
-      </c>
+        <v>-0.5637583892617449</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B19" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6813186813186813</v>
+        <v>0.7134831460674157</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5930232558139535</v>
-      </c>
+        <v>-0.5989932885906041</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="B20" t="n">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.7415730337078652</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6279069767441861</v>
-      </c>
+        <v>-0.6342281879194631</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B21" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7774725274725275</v>
+        <v>0.797752808988764</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6627906976744186</v>
-      </c>
+        <v>-0.6694630872483222</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B22" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8296703296703297</v>
+        <v>0.851123595505618</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6976744186046512</v>
-      </c>
+        <v>-0.7046979865771812</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4197,10 +6570,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="B2" t="n">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -4209,287 +6582,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8509973377068843</v>
+        <v>-0.9473455699179107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>373</v>
+        <v>420</v>
       </c>
       <c r="B3" t="n">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0332409972299169</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03398058252427184</v>
+        <v>-0.03482587064676617</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="B4" t="n">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06094182825484765</v>
+        <v>0.06617647058823529</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06796116504854369</v>
+        <v>-0.06965174129353234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>401</v>
+        <v>455</v>
       </c>
       <c r="B5" t="n">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="C5" t="n">
-        <v>0.110803324099723</v>
+        <v>0.1151960784313725</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1019417475728155</v>
+        <v>-0.1044776119402985</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="B6" t="n">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1440443213296399</v>
+        <v>0.142156862745098</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1359223300970874</v>
+        <v>-0.1393034825870647</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>426</v>
+        <v>486</v>
       </c>
       <c r="B7" t="n">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1800554016620499</v>
+        <v>0.1911764705882353</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1699029126213592</v>
+        <v>-0.1741293532338309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>441</v>
+        <v>497</v>
       </c>
       <c r="B8" t="n">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C8" t="n">
-        <v>0.221606648199446</v>
+        <v>0.2181372549019608</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2038834951456311</v>
+        <v>-0.208955223880597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>514</v>
+      </c>
+      <c r="B9" t="n">
         <v>456</v>
       </c>
-      <c r="B9" t="n">
-        <v>471</v>
-      </c>
       <c r="C9" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2598039215686275</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2378640776699029</v>
+        <v>-0.2437810945273632</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>468</v>
+        <v>524</v>
       </c>
       <c r="B10" t="n">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="C10" t="n">
-        <v>0.296398891966759</v>
+        <v>0.2843137254901961</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2718446601941747</v>
+        <v>-0.2786069651741294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>485</v>
+        <v>540</v>
       </c>
       <c r="B11" t="n">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3434903047091413</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3058252427184466</v>
+        <v>-0.3134328358208955</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>504</v>
+        <v>557</v>
       </c>
       <c r="B12" t="n">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3961218836565097</v>
+        <v>0.3651960784313725</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3398058252427185</v>
+        <v>-0.3482587064676617</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>520</v>
+        <v>577</v>
       </c>
       <c r="B13" t="n">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4404432132963989</v>
+        <v>0.4142156862745098</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3737864077669903</v>
+        <v>-0.3830845771144278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>533</v>
+        <v>592</v>
       </c>
       <c r="B14" t="n">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4764542936288089</v>
+        <v>0.4509803921568628</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4077669902912621</v>
+        <v>-0.417910447761194</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="B15" t="n">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5235457063711911</v>
+        <v>0.4852941176470588</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.441747572815534</v>
+        <v>-0.4527363184079602</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>566</v>
+        <v>619</v>
       </c>
       <c r="B16" t="n">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5678670360110804</v>
+        <v>0.5171568627450981</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4757281553398058</v>
+        <v>-0.4875621890547264</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>586</v>
+        <v>637</v>
       </c>
       <c r="B17" t="n">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6232686980609419</v>
+        <v>0.5612745098039216</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5097087378640777</v>
+        <v>-0.5223880597014925</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>600</v>
+        <v>657</v>
       </c>
       <c r="B18" t="n">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6620498614958449</v>
+        <v>0.6102941176470589</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5436893203883495</v>
+        <v>-0.5572139303482587</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>618</v>
+        <v>672</v>
       </c>
       <c r="B19" t="n">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7119113573407202</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5776699029126213</v>
+        <v>-0.5920398009950248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>636</v>
+        <v>684</v>
       </c>
       <c r="B20" t="n">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7617728531855956</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6116504854368932</v>
+        <v>-0.6268656716417911</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>655</v>
+        <v>703</v>
       </c>
       <c r="B21" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C21" t="n">
-        <v>0.814404432132964</v>
+        <v>0.7230392156862745</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6456310679611651</v>
+        <v>-0.6616915422885572</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>672</v>
+        <v>721</v>
       </c>
       <c r="B22" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8614958448753463</v>
+        <v>0.7671568627450981</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6796116504854369</v>
+        <v>-0.6965174129353234</v>
       </c>
     </row>
   </sheetData>
@@ -4535,10 +6908,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="B2" t="n">
-        <v>600</v>
+        <v>564</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -4547,287 +6920,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.762015074995108</v>
+        <v>-1.676424585734612</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="B3" t="n">
-        <v>635</v>
+        <v>599</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02790697674418605</v>
+        <v>-0.04466501240694789</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05833333333333333</v>
+        <v>0.06205673758865248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="B4" t="n">
-        <v>670</v>
+        <v>634</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.07441860465116279</v>
+        <v>-0.07444168734491315</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.124113475177305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B5" t="n">
-        <v>705</v>
+        <v>669</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1186046511627907</v>
+        <v>-0.119106699751861</v>
       </c>
       <c r="D5" t="n">
-        <v>0.175</v>
+        <v>0.1861702127659574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="B6" t="n">
-        <v>740</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1418604651162791</v>
+        <v>-0.1662531017369727</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2482269503546099</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="B7" t="n">
-        <v>775</v>
+        <v>739</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.172093023255814</v>
+        <v>-0.2084367245657568</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3102836879432624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="B8" t="n">
-        <v>810</v>
+        <v>774</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.213953488372093</v>
+        <v>-0.2382133995037221</v>
       </c>
       <c r="D8" t="n">
-        <v>0.35</v>
+        <v>0.3723404255319149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="B9" t="n">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2488372093023256</v>
+        <v>-0.2704714640198511</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4083333333333333</v>
+        <v>0.4343971631205674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="B10" t="n">
-        <v>880</v>
+        <v>844</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2790697674418605</v>
+        <v>-0.3200992555831266</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4964539007092199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="B11" t="n">
-        <v>915</v>
+        <v>879</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3046511627906976</v>
+        <v>-0.3622828784119106</v>
       </c>
       <c r="D11" t="n">
-        <v>0.525</v>
+        <v>0.5585106382978723</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="B12" t="n">
-        <v>950</v>
+        <v>914</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3279069767441861</v>
+        <v>-0.3870967741935484</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6205673758865248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="B13" t="n">
-        <v>985</v>
+        <v>949</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3604651162790697</v>
+        <v>-0.4218362282878412</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6416666666666667</v>
+        <v>0.6826241134751773</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="B14" t="n">
-        <v>1020</v>
+        <v>984</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.386046511627907</v>
+        <v>-0.4540942928039702</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7</v>
+        <v>0.7446808510638298</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="B15" t="n">
-        <v>1055</v>
+        <v>1019</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4302325581395349</v>
+        <v>-0.5012406947890818</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7583333333333333</v>
+        <v>0.8067375886524822</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B16" t="n">
-        <v>1090</v>
+        <v>1054</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.4558139534883721</v>
+        <v>-0.5459057071960298</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.8687943262411347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="B17" t="n">
-        <v>1125</v>
+        <v>1089</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.5023255813953489</v>
+        <v>-0.5781637717121588</v>
       </c>
       <c r="D17" t="n">
-        <v>0.875</v>
+        <v>0.9308510638297872</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="B18" t="n">
-        <v>1160</v>
+        <v>1124</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.5441860465116279</v>
+        <v>-0.6029776674937966</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9929078014184397</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="B19" t="n">
-        <v>1195</v>
+        <v>1159</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5697674418604651</v>
+        <v>-0.6401985111662531</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9916666666666667</v>
+        <v>1.054964539007092</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="B20" t="n">
-        <v>1230</v>
+        <v>1194</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.6</v>
+        <v>-0.6774193548387096</v>
       </c>
       <c r="D20" t="n">
-        <v>1.05</v>
+        <v>1.117021276595745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="B21" t="n">
-        <v>1265</v>
+        <v>1229</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.6372093023255814</v>
+        <v>-0.7146401985111662</v>
       </c>
       <c r="D21" t="n">
-        <v>1.108333333333333</v>
+        <v>1.179078014184397</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="B22" t="n">
-        <v>1300</v>
+        <v>1264</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.6813953488372093</v>
+        <v>-0.739454094292804</v>
       </c>
       <c r="D22" t="n">
-        <v>1.166666666666667</v>
+        <v>1.24113475177305</v>
       </c>
     </row>
   </sheetData>
@@ -4873,10 +7246,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="B2" t="n">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -4885,287 +7258,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7155759517068527</v>
+        <v>-0.7576476427473858</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B3" t="n">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03044496487119438</v>
+        <v>0.04600484261501211</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02791461412151067</v>
+        <v>-0.02698412698412699</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="B4" t="n">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07025761124121779</v>
+        <v>0.08232445520581114</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05582922824302135</v>
+        <v>-0.05396825396825397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="B5" t="n">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1124121779859485</v>
+        <v>0.1162227602905569</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08374384236453201</v>
+        <v>-0.08095238095238096</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B6" t="n">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1381733021077283</v>
+        <v>0.1549636803874092</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1116584564860427</v>
+        <v>-0.1079365079365079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="B7" t="n">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1850117096018735</v>
+        <v>0.1791767554479419</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1395730706075534</v>
+        <v>-0.1349206349206349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="B8" t="n">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2295081967213115</v>
+        <v>0.2276029055690073</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.167487684729064</v>
+        <v>-0.1619047619047619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="B9" t="n">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2622950819672131</v>
+        <v>0.261501210653753</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1954022988505747</v>
+        <v>-0.1888888888888889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="B10" t="n">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2997658079625293</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2233169129720854</v>
+        <v>-0.2158730158730159</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="B11" t="n">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3466042154566745</v>
+        <v>0.3341404358353511</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2512315270935961</v>
+        <v>-0.2428571428571429</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="B12" t="n">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3793911007025761</v>
+        <v>0.3680387409200969</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2791461412151067</v>
+        <v>-0.2698412698412698</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="B13" t="n">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4262295081967213</v>
+        <v>0.3995157384987894</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3070607553366174</v>
+        <v>-0.2968253968253968</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>626</v>
+        <v>591</v>
       </c>
       <c r="B14" t="n">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4660421545667447</v>
+        <v>0.4309927360774818</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3349753694581281</v>
+        <v>-0.3238095238095238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>640</v>
+        <v>607</v>
       </c>
       <c r="B15" t="n">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4988290398126464</v>
+        <v>0.4697336561743342</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3628899835796388</v>
+        <v>-0.3507936507936508</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>657</v>
+        <v>626</v>
       </c>
       <c r="B16" t="n">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5386416861826698</v>
+        <v>0.5157384987893463</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3908045977011494</v>
+        <v>-0.3777777777777778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>673</v>
+        <v>641</v>
       </c>
       <c r="B17" t="n">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5761124121779859</v>
+        <v>0.5520581113801453</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4187192118226601</v>
+        <v>-0.4047619047619048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>684</v>
+        <v>651</v>
       </c>
       <c r="B18" t="n">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6018735362997658</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4466338259441708</v>
+        <v>-0.4317460317460318</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>702</v>
+        <v>668</v>
       </c>
       <c r="B19" t="n">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6440281030444965</v>
+        <v>0.6174334140435835</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4745484400656814</v>
+        <v>-0.4587301587301587</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>721</v>
+        <v>685</v>
       </c>
       <c r="B20" t="n">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6885245901639344</v>
+        <v>0.6585956416464891</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5024630541871922</v>
+        <v>-0.4857142857142857</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>738</v>
+        <v>705</v>
       </c>
       <c r="B21" t="n">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7283372365339579</v>
+        <v>0.7070217917675545</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5303776683087028</v>
+        <v>-0.5126984126984127</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>753</v>
+        <v>723</v>
       </c>
       <c r="B22" t="n">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7634660421545667</v>
+        <v>0.7506053268765133</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5582922824302134</v>
+        <v>-0.5396825396825397</v>
       </c>
     </row>
   </sheetData>
@@ -5211,10 +7584,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>372</v>
+        <v>411</v>
       </c>
       <c r="B2" t="n">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -5223,287 +7596,287 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8632511909659254</v>
+        <v>-0.9710470351105253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="B3" t="n">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.0291970802919708</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03595890410958904</v>
+        <v>-0.03658536585365853</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>402</v>
+        <v>437</v>
       </c>
       <c r="B4" t="n">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.06326034063260341</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07191780821917808</v>
+        <v>-0.07317073170731707</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="B5" t="n">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1075268817204301</v>
+        <v>0.1046228710462287</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1078767123287671</v>
+        <v>-0.1097560975609756</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>430</v>
+        <v>471</v>
       </c>
       <c r="B6" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1559139784946237</v>
+        <v>0.145985401459854</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1438356164383562</v>
+        <v>-0.1463414634146341</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2043010752688172</v>
+        <v>0.1824817518248175</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1797945205479452</v>
+        <v>-0.1829268292682927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="B8" t="n">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C8" t="n">
-        <v>0.239247311827957</v>
+        <v>0.2141119221411192</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2157534246575342</v>
+        <v>-0.2195121951219512</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="B9" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2768817204301075</v>
+        <v>0.2554744525547445</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2517123287671233</v>
+        <v>-0.2560975609756098</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="B10" t="n">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3279569892473118</v>
+        <v>0.2895377128953771</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2876712328767123</v>
+        <v>-0.2926829268292683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="B11" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3790322580645161</v>
+        <v>0.3260340632603406</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3236301369863014</v>
+        <v>-0.3292682926829268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="B12" t="n">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.3722627737226277</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3595890410958904</v>
+        <v>-0.3658536585365854</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="B13" t="n">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4569892473118279</v>
+        <v>0.413625304136253</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3955479452054795</v>
+        <v>-0.4024390243902439</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="B14" t="n">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C14" t="n">
-        <v>0.489247311827957</v>
+        <v>0.4476885644768857</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4315068493150685</v>
+        <v>-0.4390243902439024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="B15" t="n">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5241935483870968</v>
+        <v>0.4744525547445255</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4674657534246575</v>
+        <v>-0.475609756097561</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="B16" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5752688172043011</v>
+        <v>0.5182481751824818</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5034246575342466</v>
+        <v>-0.5121951219512195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>604</v>
+        <v>637</v>
       </c>
       <c r="B17" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6236559139784946</v>
+        <v>0.5498783454987834</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5393835616438356</v>
+        <v>-0.5487804878048781</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>624</v>
+        <v>654</v>
       </c>
       <c r="B18" t="n">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.5912408759124088</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5753424657534246</v>
+        <v>-0.5853658536585366</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="B19" t="n">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C19" t="n">
-        <v>0.728494623655914</v>
+        <v>0.6399026763990268</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6113013698630136</v>
+        <v>-0.6219512195121951</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="B20" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C20" t="n">
-        <v>0.760752688172043</v>
+        <v>0.683698296836983</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6472602739726028</v>
+        <v>-0.6585365853658537</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>673</v>
+        <v>706</v>
       </c>
       <c r="B21" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8091397849462365</v>
+        <v>0.7177615571776156</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6832191780821918</v>
+        <v>-0.6951219512195121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>683</v>
+        <v>719</v>
       </c>
       <c r="B22" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8360215053763441</v>
+        <v>0.7493917274939172</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7191780821917808</v>
+        <v>-0.7317073170731707</v>
       </c>
     </row>
   </sheetData>
